--- a/ES_NQ_STAT_PCA_RESULTS 60 min 3.xlsx
+++ b/ES_NQ_STAT_PCA_RESULTS 60 min 3.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Trades" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Charts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charts" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -142,13 +142,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
